--- a/nr-update-system-nss/ig/StructureDefinition-fr-core-organization-uac.xlsx
+++ b/nr-update-system-nss/ig/StructureDefinition-fr-core-organization-uac.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-22T17:34:51+00:00</t>
+    <t>2026-02-23T07:43:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-update-system-nss/ig/StructureDefinition-fr-core-organization-uac.xlsx
+++ b/nr-update-system-nss/ig/StructureDefinition-fr-core-organization-uac.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.2.0-ballot-2</t>
+    <t>2.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T10:28:50+00:00</t>
+    <t>2026-03-25T14:42:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization|2.2.0-ballot-2</t>
+    <t>https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization|2.2.0</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -630,7 +630,7 @@
     <t>shortName</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization-short-name|2.2.0-ballot-2}
+    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization-short-name|2.2.0}
 </t>
   </si>
   <si>
@@ -701,14 +701,14 @@
     <t>member</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization-member|2.2.0-ballot-2}
+    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization-member|2.2.0}
 </t>
   </si>
   <si>
-    <t>FR Core Organization Extension - Membre d'organisation</t>
-  </si>
-  <si>
-    <t>Extension permettant de définir des membres d'une organisation.</t>
+    <t>FR Core Organization Extension - quelles sont les entités qui font partie de l'organisation</t>
+  </si>
+  <si>
+    <t>Extension permettant de définir des membres d'une organisation. Les membres sont des organisations filles de la ressources. C'est la relation inverse de partOf.</t>
   </si>
   <si>
     <t>Organization.extension:disciplinePrestation</t>
@@ -717,7 +717,7 @@
     <t>disciplinePrestation</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization-discipline-prestation|2.2.0-ballot-2}
+    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization-discipline-prestation|2.2.0}
 </t>
   </si>
   <si>
@@ -733,7 +733,7 @@
     <t>tarif</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization-tarif|2.2.0-ballot-2}
+    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization-tarif|2.2.0}
 </t>
   </si>
   <si>
@@ -855,7 +855,7 @@
 &lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-organization-type|2.2.0-ballot-2</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-organization-type|2.2.0</t>
   </si>
   <si>
     <t>No equivalent in v2</t>
@@ -910,7 +910,7 @@
     <t>Organization.telecom</t>
   </si>
   <si>
-    <t xml:space="preserve">ContactPoint {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-contact-point|2.2.0-ballot-2}
+    <t xml:space="preserve">ContactPoint {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-contact-point|2.2.0}
 </t>
   </si>
   <si>
@@ -946,7 +946,7 @@
     <t>Organization.address</t>
   </si>
   <si>
-    <t xml:space="preserve">Address {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-address|2.2.0-ballot-2}
+    <t xml:space="preserve">Address {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-address|2.2.0}
 </t>
   </si>
   <si>
@@ -982,7 +982,7 @@
     <t>Organization.partOf</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization-uf|2.2.0-ballot-2)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization-uf|2.2.0)
 </t>
   </si>
   <si>
@@ -1535,7 +1535,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="89.1796875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="82.6328125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1550,7 +1550,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="84.54296875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="60.875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="54.33203125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
@@ -4210,7 +4210,7 @@
         <v>79</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>78</v>
